--- a/dist/AMT Taxonomy - Product Interest Category.xlsx
+++ b/dist/AMT Taxonomy - Product Interest Category.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,9 +56,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,6 +436,10 @@
   </sheetPr>
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="99" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -429,7 +447,7 @@
           <t>Taxonomy name:</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Visitor View of Product Categories</t>
         </is>
@@ -441,7 +459,7 @@
           <t>Taxonomy owner:</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Chris Downs</t>
         </is>
@@ -453,7 +471,7 @@
           <t>Status:</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -465,7 +483,7 @@
           <t>Governers:</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Allison, Ryan, Downs</t>
         </is>
@@ -477,7 +495,7 @@
           <t>Consumers:</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Kristin, Mark K, Jess, Allison, Downs, Alka, Kalesh</t>
         </is>
@@ -489,7 +507,7 @@
           <t>Tech stewards:</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Shaurabh</t>
         </is>
@@ -501,7 +519,7 @@
           <t>Related products:</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>IMTS (visitor reg and exhibitor categories/showrooms), Passport, Media Sponsorships (media kit)</t>
         </is>
@@ -513,7 +531,7 @@
           <t>Related systems/databases:</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Maritz, Hubspot, Data warehouse, Passport, Exhibitor Space Application (linked at major category)</t>
         </is>
@@ -525,7 +543,7 @@
           <t>Next update date:</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -537,9 +555,9 @@
           <t>Related documentation:</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://amtonline.sharepoint.com/sites/governance/Shared%20Documents/Taxonomy%20Change%20Process.docx</t>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Taxonomy Change Process_DRAFT.docx</t>
         </is>
       </c>
     </row>
@@ -549,7 +567,7 @@
           <t>Use cases:</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Marketing uses this for targeted marketing</t>
         </is>
@@ -557,7 +575,7 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Passport uses this as a filter to create lists</t>
         </is>
@@ -565,7 +583,7 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>IMTS uses this as a demographic field for visitor registration</t>
         </is>
@@ -573,7 +591,7 @@
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>IMTS uses this in post-show reporting</t>
         </is>
@@ -581,7 +599,7 @@
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>IMTS uses this to create exhibitor product categories</t>
         </is>
@@ -593,9 +611,12 @@
           <t>Notes:</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -608,6 +629,17 @@
   </sheetPr>
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="120" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -620,7 +652,7 @@
           <t>Release Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Scope Summary</t>
         </is>
@@ -667,7 +699,7 @@
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Initial release — visitor view of product categories with bucket hierarchy and SHACL validation against the pc: taxonomy.</t>
         </is>
@@ -682,13 +714,16 @@
           <t>Draft</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://github.com/ManufacturingTechnology/amt-ontology/releases/tag/v0.1.0</t>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -701,6 +736,13 @@
   </sheetPr>
   <dimension ref="A1:E158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3125,6 +3167,9 @@
   </sheetPr>
   <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
